--- a/sample/患者マスタ_サンプル.xlsx
+++ b/sample/患者マスタ_サンプル.xlsx
@@ -420,7 +420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L14"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -430,9 +430,10 @@
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="32.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,9 +470,12 @@
         <v>住所2</v>
       </c>
       <c r="J2" t="str">
+        <v>グループホーム</v>
+      </c>
+      <c r="K2" t="str">
         <v>電話番号</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>主治医</v>
       </c>
     </row>
@@ -504,9 +508,12 @@
         <v/>
       </c>
       <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
         <v>03-0000-0001</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>佐藤</v>
       </c>
     </row>
@@ -539,9 +546,12 @@
         <v>メゾン神宮前101</v>
       </c>
       <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>03-0000-0002</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>佐藤</v>
       </c>
     </row>
@@ -574,9 +584,12 @@
         <v/>
       </c>
       <c r="J5" t="str">
+        <v>グループホームさくら</v>
+      </c>
+      <c r="K5" t="str">
         <v>03-0000-0003</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
         <v>田中</v>
       </c>
     </row>
@@ -609,9 +622,12 @@
         <v>サンシャイン荘2F</v>
       </c>
       <c r="J6" t="str">
+        <v>グループホームさくら</v>
+      </c>
+      <c r="K6" t="str">
         <v>03-0000-0004</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <v>田中</v>
       </c>
     </row>
@@ -644,9 +660,12 @@
         <v/>
       </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>03-0000-0005</v>
       </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
         <v>佐藤</v>
       </c>
     </row>
@@ -679,15 +698,246 @@
         <v/>
       </c>
       <c r="J8" t="str">
+        <v>グループホームあおば</v>
+      </c>
+      <c r="K8" t="str">
         <v>03-0000-0006</v>
       </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
         <v>田中</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>002031</v>
+      </c>
+      <c r="B9" t="str">
+        <v>39130011</v>
+      </c>
+      <c r="C9" t="str">
+        <v>渡辺 清</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ワタナベ キヨシ</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>13913</v>
+      </c>
+      <c r="G9" t="str">
+        <v>190-0012</v>
+      </c>
+      <c r="H9" t="str">
+        <v>東京都立川市曙町2丁目一番地の十三</v>
+      </c>
+      <c r="I9" t="str">
+        <v>パークサイドレジデンス立川北口ウエストタワー1205号室</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>03-0000-0007</v>
+      </c>
+      <c r="L9" t="str">
+        <v>田中</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>002045</v>
+      </c>
+      <c r="B10" t="str">
+        <v>06130012</v>
+      </c>
+      <c r="C10" t="str">
+        <v>小林 トメ</v>
+      </c>
+      <c r="D10" t="str">
+        <v>コバヤシ トメ</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10845</v>
+      </c>
+      <c r="G10" t="str">
+        <v>185-0012</v>
+      </c>
+      <c r="H10" t="str">
+        <v>東京都国分寺市本町3-3-3</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>グループホームあおば</v>
+      </c>
+      <c r="K10" t="str">
+        <v>03-0000-0008</v>
+      </c>
+      <c r="L10" t="str">
+        <v>佐藤</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>002050</v>
+      </c>
+      <c r="B11" t="str">
+        <v>06130012</v>
+      </c>
+      <c r="C11" t="str">
+        <v>加藤 茂</v>
+      </c>
+      <c r="D11" t="str">
+        <v>カトウ シゲル</v>
+      </c>
+      <c r="E11" t="str">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>15831</v>
+      </c>
+      <c r="G11" t="str">
+        <v>181-0013</v>
+      </c>
+      <c r="H11" t="str">
+        <v>東京都三鷹市下連雀3-1-1</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>03-0000-0009</v>
+      </c>
+      <c r="L11" t="str">
+        <v>佐藤</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>002061</v>
+      </c>
+      <c r="B12" t="str">
+        <v>39130011</v>
+      </c>
+      <c r="C12" t="str">
+        <v>吉田 和子</v>
+      </c>
+      <c r="D12" t="str">
+        <v>ヨシダ カズコ</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>13485</v>
+      </c>
+      <c r="G12" t="str">
+        <v>182-0024</v>
+      </c>
+      <c r="H12" t="str">
+        <v>東京都調布市布田1-2-3</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>グループホームさくら</v>
+      </c>
+      <c r="K12" t="str">
+        <v>03-0000-0010</v>
+      </c>
+      <c r="L12" t="str">
+        <v>田中</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>002077</v>
+      </c>
+      <c r="B13" t="str">
+        <v>39130011</v>
+      </c>
+      <c r="C13" t="str">
+        <v>山本 勇</v>
+      </c>
+      <c r="D13" t="str">
+        <v>ヤマモト イサム</v>
+      </c>
+      <c r="E13" t="str">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>12646</v>
+      </c>
+      <c r="G13" t="str">
+        <v>183-0023</v>
+      </c>
+      <c r="H13" t="str">
+        <v>東京都府中市宮町1-1</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>03-0000-0011</v>
+      </c>
+      <c r="L13" t="str">
+        <v>田中</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>002088</v>
+      </c>
+      <c r="B14" t="str">
+        <v>06130012</v>
+      </c>
+      <c r="C14" t="str">
+        <v>中村 静江</v>
+      </c>
+      <c r="D14" t="str">
+        <v>ナカムラ シズエ</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>15038</v>
+      </c>
+      <c r="G14" t="str">
+        <v>187-0002</v>
+      </c>
+      <c r="H14" t="str">
+        <v>東京都小平市花小金井1-1-1</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>03-0000-0012</v>
+      </c>
+      <c r="L14" t="str">
+        <v>佐藤</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>